--- a/e2e/expectedData/rekap_bayar_Bayar_Gaji_2026-01.xlsx
+++ b/e2e/expectedData/rekap_bayar_Bayar_Gaji_2026-01.xlsx
@@ -71,184 +71,184 @@
     <t>TOTAL</t>
   </si>
   <si>
+    <t>DIAN EVIYANTI APLUGI</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>$ 314.94</t>
+  </si>
+  <si>
+    <t>$ 300.00</t>
+  </si>
+  <si>
+    <t>$ 0.00</t>
+  </si>
+  <si>
+    <t>$ 75.00</t>
+  </si>
+  <si>
+    <t>$ 689.94</t>
+  </si>
+  <si>
+    <t>AHMAD RIYANA SAPUTRA</t>
+  </si>
+  <si>
+    <t>$ 521.00</t>
+  </si>
+  <si>
+    <t>$ 520.00</t>
+  </si>
+  <si>
+    <t>$ 1,650.00</t>
+  </si>
+  <si>
+    <t>$ 260.00</t>
+  </si>
+  <si>
+    <t>$ 4,601.00</t>
+  </si>
+  <si>
+    <t>CLAUDIO DA COSTA ALVES</t>
+  </si>
+  <si>
+    <t>$ 219.26</t>
+  </si>
+  <si>
+    <t>$ 210.00</t>
+  </si>
+  <si>
+    <t>$ 52.50</t>
+  </si>
+  <si>
+    <t>$ 481.76</t>
+  </si>
+  <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>$ 455.00</t>
+  </si>
+  <si>
+    <t>$ 340.00</t>
+  </si>
+  <si>
+    <t>$ 85.00</t>
+  </si>
+  <si>
+    <t>$ 63.75</t>
+  </si>
+  <si>
+    <t>$ 4,243.75</t>
+  </si>
+  <si>
+    <t>FRIESCA AMELIA</t>
+  </si>
+  <si>
+    <t>$ 701.00</t>
+  </si>
+  <si>
+    <t>$ 700.00</t>
+  </si>
+  <si>
+    <t>$ 175.00</t>
+  </si>
+  <si>
+    <t>$ 1,576.00</t>
+  </si>
+  <si>
+    <t>RIMBUN SIBURIAN</t>
+  </si>
+  <si>
+    <t>$ 1,189.08</t>
+  </si>
+  <si>
+    <t>$ 1,050.00</t>
+  </si>
+  <si>
+    <t>$ 2,839.08</t>
+  </si>
+  <si>
+    <t>LESTARI PUTRI CANTIKA</t>
+  </si>
+  <si>
+    <t>Transfer</t>
+  </si>
+  <si>
+    <t>BSI</t>
+  </si>
+  <si>
+    <t>$ 460.00</t>
+  </si>
+  <si>
+    <t>$ 404.00</t>
+  </si>
+  <si>
+    <t>$ 126.00</t>
+  </si>
+  <si>
+    <t>$ 989.00</t>
+  </si>
+  <si>
+    <t>HERU YULIANTO</t>
+  </si>
+  <si>
+    <t>$ 696.65</t>
+  </si>
+  <si>
+    <t>$ 1,100.00</t>
+  </si>
+  <si>
+    <t>$ 3,771.65</t>
+  </si>
+  <si>
+    <t>SYALDY KHARISMA ANANDA</t>
+  </si>
+  <si>
+    <t>$ 380.52</t>
+  </si>
+  <si>
+    <t>$ 200.00</t>
+  </si>
+  <si>
+    <t>$ 1,155.52</t>
+  </si>
+  <si>
+    <t>AGOSTINHO GOMES FERNANDES</t>
+  </si>
+  <si>
+    <t>$ -1,189.00</t>
+  </si>
+  <si>
+    <t>$ 160.00</t>
+  </si>
+  <si>
+    <t>$ 140.00</t>
+  </si>
+  <si>
+    <t>$ -289.00</t>
+  </si>
+  <si>
     <t>ADROALDINO DA SILVA NORONHA TOME</t>
   </si>
   <si>
-    <t>Cash</t>
-  </si>
-  <si>
-    <t>2026-01</t>
-  </si>
-  <si>
     <t>$ 326.44</t>
   </si>
   <si>
     <t>$ 180.00</t>
   </si>
   <si>
-    <t>$ 1,100.00</t>
-  </si>
-  <si>
     <t>$ 22.50</t>
   </si>
   <si>
-    <t>$ 0.00</t>
-  </si>
-  <si>
     <t>$ 2,728.94</t>
   </si>
   <si>
-    <t>AGOSTINHO GOMES FERNANDES</t>
-  </si>
-  <si>
-    <t>$ -1,189.00</t>
-  </si>
-  <si>
-    <t>$ 160.00</t>
-  </si>
-  <si>
-    <t>$ 300.00</t>
-  </si>
-  <si>
-    <t>$ 140.00</t>
-  </si>
-  <si>
-    <t>$ -289.00</t>
-  </si>
-  <si>
-    <t>CELIA MARIA REGO DE FATIMA</t>
-  </si>
-  <si>
-    <t>$ 415.00</t>
-  </si>
-  <si>
-    <t>$ 340.00</t>
-  </si>
-  <si>
-    <t>$ 1,650.00</t>
-  </si>
-  <si>
-    <t>$ 85.00</t>
-  </si>
-  <si>
-    <t>$ 63.75</t>
-  </si>
-  <si>
-    <t>$ 4,203.75</t>
-  </si>
-  <si>
-    <t>CLAUDIO DA COSTA ALVES</t>
-  </si>
-  <si>
-    <t>$ 169.26</t>
-  </si>
-  <si>
-    <t>$ 210.00</t>
-  </si>
-  <si>
-    <t>$ 52.50</t>
-  </si>
-  <si>
-    <t>$ 431.76</t>
-  </si>
-  <si>
-    <t>DIAN EVIYANTI APLUGI</t>
-  </si>
-  <si>
-    <t>$ 254.94</t>
-  </si>
-  <si>
-    <t>$ 75.00</t>
-  </si>
-  <si>
-    <t>$ 629.94</t>
-  </si>
-  <si>
-    <t>AHMAD RIYANA SAPUTRA</t>
-  </si>
-  <si>
-    <t>$ 451.00</t>
-  </si>
-  <si>
-    <t>$ 520.00</t>
-  </si>
-  <si>
-    <t>$ 260.00</t>
-  </si>
-  <si>
-    <t>$ 4,531.00</t>
-  </si>
-  <si>
-    <t>FRIESCA AMELIA</t>
-  </si>
-  <si>
-    <t>$ 701.00</t>
-  </si>
-  <si>
-    <t>$ 700.00</t>
-  </si>
-  <si>
-    <t>$ 175.00</t>
-  </si>
-  <si>
-    <t>$ 1,576.00</t>
-  </si>
-  <si>
-    <t>HERU YULIANTO</t>
-  </si>
-  <si>
-    <t>$ 696.65</t>
-  </si>
-  <si>
-    <t>$ 3,771.65</t>
-  </si>
-  <si>
-    <t>RIMBUN SIBURIAN</t>
-  </si>
-  <si>
-    <t>$ -711.89</t>
-  </si>
-  <si>
-    <t>$ 1,050.00</t>
-  </si>
-  <si>
-    <t>$ 938.11</t>
-  </si>
-  <si>
-    <t>SYALDY KHARISMA ANANDA</t>
-  </si>
-  <si>
-    <t>$ 380.52</t>
-  </si>
-  <si>
-    <t>$ 200.00</t>
-  </si>
-  <si>
-    <t>$ 1,155.52</t>
-  </si>
-  <si>
-    <t>LESTARI PUTRI CANTIKA</t>
-  </si>
-  <si>
-    <t>Transfer</t>
-  </si>
-  <si>
-    <t>BSI</t>
-  </si>
-  <si>
-    <t>$ 460.00</t>
-  </si>
-  <si>
-    <t>$ 404.00</t>
-  </si>
-  <si>
-    <t>$ 126.00</t>
-  </si>
-  <si>
-    <t>$ 989.00</t>
-  </si>
-  <si>
-    <t>$ 1,953.92</t>
+    <t>$ 4,074.89</t>
   </si>
   <si>
     <t>$ 4,864.00</t>
@@ -260,10 +260,10 @@
     <t>$ 1,186.00</t>
   </si>
   <si>
-    <t>$ 20,666.67</t>
-  </si>
-  <si>
-    <t>DILI, 26 August 2026</t>
+    <t>$ 22,787.64</t>
+  </si>
+  <si>
+    <t>DILI, 09 September 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
@@ -795,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>24016</v>
+        <v>79001</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -822,10 +822,10 @@
         <v>24</v>
       </c>
       <c r="N5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" t="s">
         <v>25</v>
-      </c>
-      <c r="O5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -833,10 +833,10 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>26013</v>
+        <v>95008</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
@@ -845,25 +845,25 @@
         <v>20</v>
       </c>
       <c r="I6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" t="s">
         <v>28</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>29</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s">
         <v>30</v>
       </c>
-      <c r="L6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" t="s">
         <v>31</v>
-      </c>
-      <c r="N6" t="s">
-        <v>25</v>
-      </c>
-      <c r="O6" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -871,10 +871,10 @@
         <v>3</v>
       </c>
       <c r="B7">
-        <v>92003</v>
+        <v>24005</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
         <v>19</v>
@@ -883,25 +883,25 @@
         <v>20</v>
       </c>
       <c r="I7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" t="s">
         <v>34</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" t="s">
         <v>35</v>
       </c>
-      <c r="K7" t="s">
+      <c r="N7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" t="s">
         <v>36</v>
-      </c>
-      <c r="L7" t="s">
-        <v>36</v>
-      </c>
-      <c r="M7" t="s">
-        <v>37</v>
-      </c>
-      <c r="N7" t="s">
-        <v>38</v>
-      </c>
-      <c r="O7" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -909,10 +909,10 @@
         <v>4</v>
       </c>
       <c r="B8">
-        <v>24005</v>
+        <v>92003</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
         <v>19</v>
@@ -921,25 +921,25 @@
         <v>20</v>
       </c>
       <c r="I8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s">
+        <v>40</v>
+      </c>
+      <c r="N8" t="s">
         <v>41</v>
       </c>
-      <c r="J8" t="s">
+      <c r="O8" t="s">
         <v>42</v>
-      </c>
-      <c r="K8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" t="s">
-        <v>43</v>
-      </c>
-      <c r="N8" t="s">
-        <v>25</v>
-      </c>
-      <c r="O8" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -947,10 +947,10 @@
         <v>5</v>
       </c>
       <c r="B9">
-        <v>79001</v>
+        <v>91009</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
         <v>19</v>
@@ -959,25 +959,25 @@
         <v>20</v>
       </c>
       <c r="I9" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" t="s">
         <v>46</v>
       </c>
-      <c r="J9" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9" t="s">
         <v>47</v>
-      </c>
-      <c r="N9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O9" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -985,10 +985,10 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <v>95008</v>
+        <v>81010</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
         <v>19</v>
@@ -997,25 +997,25 @@
         <v>20</v>
       </c>
       <c r="I10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" t="s">
         <v>50</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" t="s">
+        <v>22</v>
+      </c>
+      <c r="M10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10" t="s">
         <v>51</v>
-      </c>
-      <c r="K10" t="s">
-        <v>36</v>
-      </c>
-      <c r="L10" t="s">
-        <v>36</v>
-      </c>
-      <c r="M10" t="s">
-        <v>52</v>
-      </c>
-      <c r="N10" t="s">
-        <v>25</v>
-      </c>
-      <c r="O10" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1023,17 +1023,26 @@
         <v>7</v>
       </c>
       <c r="B11">
-        <v>91009</v>
+        <v>999999</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
       </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11">
+        <v>1231414</v>
+      </c>
+      <c r="H11">
+        <v>12412414</v>
+      </c>
       <c r="I11" t="s">
         <v>55</v>
       </c>
@@ -1041,16 +1050,16 @@
         <v>56</v>
       </c>
       <c r="K11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M11" t="s">
         <v>57</v>
       </c>
       <c r="N11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O11" t="s">
         <v>58</v>
@@ -1076,22 +1085,22 @@
         <v>60</v>
       </c>
       <c r="J12" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="K12" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="L12" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="M12" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="N12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -1099,10 +1108,10 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <v>81010</v>
+        <v>91015</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
         <v>19</v>
@@ -1111,25 +1120,25 @@
         <v>20</v>
       </c>
       <c r="I13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J13" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="K13" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="L13" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="M13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -1137,10 +1146,10 @@
         <v>10</v>
       </c>
       <c r="B14">
-        <v>91015</v>
+        <v>26013</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
         <v>19</v>
@@ -1149,25 +1158,25 @@
         <v>20</v>
       </c>
       <c r="I14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J14" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="K14" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="L14" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="M14" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="N14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -1175,26 +1184,17 @@
         <v>11</v>
       </c>
       <c r="B15">
-        <v>999999</v>
+        <v>24016</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s">
         <v>20</v>
       </c>
-      <c r="F15" t="s">
-        <v>72</v>
-      </c>
-      <c r="G15">
-        <v>1231414</v>
-      </c>
-      <c r="H15">
-        <v>12412414</v>
-      </c>
       <c r="I15" t="s">
         <v>73</v>
       </c>
@@ -1202,16 +1202,16 @@
         <v>74</v>
       </c>
       <c r="K15" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="L15" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="M15" t="s">
         <v>75</v>
       </c>
       <c r="N15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O15" t="s">
         <v>76</v>
@@ -1237,7 +1237,7 @@
         <v>80</v>
       </c>
       <c r="N16" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="O16" t="s">
         <v>81</v>
@@ -1347,7 +1347,7 @@
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22" s="3" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>

--- a/e2e/expectedData/rekap_bayar_Bayar_Gaji_2026-01.xlsx
+++ b/e2e/expectedData/rekap_bayar_Bayar_Gaji_2026-01.xlsx
@@ -71,184 +71,184 @@
     <t>TOTAL</t>
   </si>
   <si>
+    <t>AGOSTINHO GOMES FERNANDES</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>$ -1,189.00</t>
+  </si>
+  <si>
+    <t>$ 160.00</t>
+  </si>
+  <si>
+    <t>$ 300.00</t>
+  </si>
+  <si>
+    <t>$ 140.00</t>
+  </si>
+  <si>
+    <t>$ 0.00</t>
+  </si>
+  <si>
+    <t>$ -289.00</t>
+  </si>
+  <si>
+    <t>ADROALDINO DA SILVA NORONHA TOME</t>
+  </si>
+  <si>
+    <t>$ 319.24</t>
+  </si>
+  <si>
+    <t>$ 180.00</t>
+  </si>
+  <si>
+    <t>$ 1,100.00</t>
+  </si>
+  <si>
+    <t>$ 22.50</t>
+  </si>
+  <si>
+    <t>$ 2,721.74</t>
+  </si>
+  <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>$ 401.40</t>
+  </si>
+  <si>
+    <t>$ 340.00</t>
+  </si>
+  <si>
+    <t>$ 1,650.00</t>
+  </si>
+  <si>
+    <t>$ 85.00</t>
+  </si>
+  <si>
+    <t>$ 63.75</t>
+  </si>
+  <si>
+    <t>$ 4,190.15</t>
+  </si>
+  <si>
+    <t>FRIESCA AMELIA</t>
+  </si>
+  <si>
+    <t>$ 701.00</t>
+  </si>
+  <si>
+    <t>$ 700.00</t>
+  </si>
+  <si>
+    <t>$ 175.00</t>
+  </si>
+  <si>
+    <t>$ 1,576.00</t>
+  </si>
+  <si>
+    <t>LESTARI PUTRI CANTIKA</t>
+  </si>
+  <si>
+    <t>Transfer</t>
+  </si>
+  <si>
+    <t>BSI</t>
+  </si>
+  <si>
+    <t>$ 460.00</t>
+  </si>
+  <si>
+    <t>$ 404.00</t>
+  </si>
+  <si>
+    <t>$ 126.00</t>
+  </si>
+  <si>
+    <t>$ 989.00</t>
+  </si>
+  <si>
+    <t>HERU YULIANTO</t>
+  </si>
+  <si>
+    <t>$ 696.65</t>
+  </si>
+  <si>
+    <t>$ 3,771.65</t>
+  </si>
+  <si>
+    <t>SYALDY KHARISMA ANANDA</t>
+  </si>
+  <si>
+    <t>$ 380.52</t>
+  </si>
+  <si>
+    <t>$ 200.00</t>
+  </si>
+  <si>
+    <t>$ 75.00</t>
+  </si>
+  <si>
+    <t>$ 1,155.52</t>
+  </si>
+  <si>
+    <t>CLAUDIO DA COSTA ALVES</t>
+  </si>
+  <si>
+    <t>$ 160.86</t>
+  </si>
+  <si>
+    <t>$ 210.00</t>
+  </si>
+  <si>
+    <t>$ 52.50</t>
+  </si>
+  <si>
+    <t>$ 423.36</t>
+  </si>
+  <si>
     <t>DIAN EVIYANTI APLUGI</t>
   </si>
   <si>
-    <t>Cash</t>
-  </si>
-  <si>
-    <t>2026-01</t>
-  </si>
-  <si>
-    <t>$ 314.94</t>
-  </si>
-  <si>
-    <t>$ 300.00</t>
-  </si>
-  <si>
-    <t>$ 0.00</t>
-  </si>
-  <si>
-    <t>$ 75.00</t>
-  </si>
-  <si>
-    <t>$ 689.94</t>
+    <t>$ 242.94</t>
+  </si>
+  <si>
+    <t>$ 617.94</t>
   </si>
   <si>
     <t>AHMAD RIYANA SAPUTRA</t>
   </si>
   <si>
-    <t>$ 521.00</t>
+    <t>$ 430.20</t>
   </si>
   <si>
     <t>$ 520.00</t>
   </si>
   <si>
-    <t>$ 1,650.00</t>
-  </si>
-  <si>
     <t>$ 260.00</t>
   </si>
   <si>
-    <t>$ 4,601.00</t>
-  </si>
-  <si>
-    <t>CLAUDIO DA COSTA ALVES</t>
-  </si>
-  <si>
-    <t>$ 219.26</t>
-  </si>
-  <si>
-    <t>$ 210.00</t>
-  </si>
-  <si>
-    <t>$ 52.50</t>
-  </si>
-  <si>
-    <t>$ 481.76</t>
-  </si>
-  <si>
-    <t>CELIA MARIA REGO DE FATIMA</t>
-  </si>
-  <si>
-    <t>$ 455.00</t>
-  </si>
-  <si>
-    <t>$ 340.00</t>
-  </si>
-  <si>
-    <t>$ 85.00</t>
-  </si>
-  <si>
-    <t>$ 63.75</t>
-  </si>
-  <si>
-    <t>$ 4,243.75</t>
-  </si>
-  <si>
-    <t>FRIESCA AMELIA</t>
-  </si>
-  <si>
-    <t>$ 701.00</t>
-  </si>
-  <si>
-    <t>$ 700.00</t>
-  </si>
-  <si>
-    <t>$ 175.00</t>
-  </si>
-  <si>
-    <t>$ 1,576.00</t>
+    <t>$ 4,510.20</t>
   </si>
   <si>
     <t>RIMBUN SIBURIAN</t>
   </si>
   <si>
-    <t>$ 1,189.08</t>
+    <t>$ -560.92</t>
   </si>
   <si>
     <t>$ 1,050.00</t>
   </si>
   <si>
-    <t>$ 2,839.08</t>
-  </si>
-  <si>
-    <t>LESTARI PUTRI CANTIKA</t>
-  </si>
-  <si>
-    <t>Transfer</t>
-  </si>
-  <si>
-    <t>BSI</t>
-  </si>
-  <si>
-    <t>$ 460.00</t>
-  </si>
-  <si>
-    <t>$ 404.00</t>
-  </si>
-  <si>
-    <t>$ 126.00</t>
-  </si>
-  <si>
-    <t>$ 989.00</t>
-  </si>
-  <si>
-    <t>HERU YULIANTO</t>
-  </si>
-  <si>
-    <t>$ 696.65</t>
-  </si>
-  <si>
-    <t>$ 1,100.00</t>
-  </si>
-  <si>
-    <t>$ 3,771.65</t>
-  </si>
-  <si>
-    <t>SYALDY KHARISMA ANANDA</t>
-  </si>
-  <si>
-    <t>$ 380.52</t>
-  </si>
-  <si>
-    <t>$ 200.00</t>
-  </si>
-  <si>
-    <t>$ 1,155.52</t>
-  </si>
-  <si>
-    <t>AGOSTINHO GOMES FERNANDES</t>
-  </si>
-  <si>
-    <t>$ -1,189.00</t>
-  </si>
-  <si>
-    <t>$ 160.00</t>
-  </si>
-  <si>
-    <t>$ 140.00</t>
-  </si>
-  <si>
-    <t>$ -289.00</t>
-  </si>
-  <si>
-    <t>ADROALDINO DA SILVA NORONHA TOME</t>
-  </si>
-  <si>
-    <t>$ 326.44</t>
-  </si>
-  <si>
-    <t>$ 180.00</t>
-  </si>
-  <si>
-    <t>$ 22.50</t>
-  </si>
-  <si>
-    <t>$ 2,728.94</t>
-  </si>
-  <si>
-    <t>$ 4,074.89</t>
+    <t>$ 1,089.08</t>
+  </si>
+  <si>
+    <t>$ 2,042.89</t>
   </si>
   <si>
     <t>$ 4,864.00</t>
@@ -260,10 +260,10 @@
     <t>$ 1,186.00</t>
   </si>
   <si>
-    <t>$ 22,787.64</t>
-  </si>
-  <si>
-    <t>DILI, 09 September 2026</t>
+    <t>$ 20,755.64</t>
+  </si>
+  <si>
+    <t>DILI, 10 September 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
@@ -795,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>79001</v>
+        <v>26013</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -822,10 +822,10 @@
         <v>24</v>
       </c>
       <c r="N5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -833,10 +833,10 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>95008</v>
+        <v>24016</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
@@ -845,25 +845,25 @@
         <v>20</v>
       </c>
       <c r="I6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -871,10 +871,10 @@
         <v>3</v>
       </c>
       <c r="B7">
-        <v>24005</v>
+        <v>92003</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
         <v>19</v>
@@ -883,25 +883,25 @@
         <v>20</v>
       </c>
       <c r="I7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K7" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="L7" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="M7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="O7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -909,10 +909,10 @@
         <v>4</v>
       </c>
       <c r="B8">
-        <v>92003</v>
+        <v>91009</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
         <v>19</v>
@@ -921,25 +921,25 @@
         <v>20</v>
       </c>
       <c r="I8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="M8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="N8" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="O8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -947,37 +947,46 @@
         <v>5</v>
       </c>
       <c r="B9">
-        <v>91009</v>
+        <v>999999</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
       </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9">
+        <v>1231414</v>
+      </c>
+      <c r="H9">
+        <v>12412414</v>
+      </c>
       <c r="I9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="N9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -985,10 +994,10 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <v>81010</v>
+        <v>74003</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
         <v>19</v>
@@ -997,25 +1006,25 @@
         <v>20</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J10" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="K10" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="L10" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M10" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="N10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1023,46 +1032,37 @@
         <v>7</v>
       </c>
       <c r="B11">
-        <v>999999</v>
+        <v>91015</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
       </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11">
-        <v>1231414</v>
-      </c>
-      <c r="H11">
-        <v>12412414</v>
-      </c>
       <c r="I11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J11" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="K11" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="L11" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="M11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1070,10 +1070,10 @@
         <v>8</v>
       </c>
       <c r="B12">
-        <v>74003</v>
+        <v>24005</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s">
         <v>19</v>
@@ -1082,25 +1082,25 @@
         <v>20</v>
       </c>
       <c r="I12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J12" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="K12" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="L12" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="M12" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="N12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -1108,10 +1108,10 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <v>91015</v>
+        <v>79001</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
         <v>19</v>
@@ -1120,25 +1120,25 @@
         <v>20</v>
       </c>
       <c r="I13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K13" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="L13" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="M13" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="N13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -1146,10 +1146,10 @@
         <v>10</v>
       </c>
       <c r="B14">
-        <v>26013</v>
+        <v>95008</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
         <v>19</v>
@@ -1158,25 +1158,25 @@
         <v>20</v>
       </c>
       <c r="I14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K14" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="L14" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="M14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -1184,10 +1184,10 @@
         <v>11</v>
       </c>
       <c r="B15">
-        <v>24016</v>
+        <v>81010</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
         <v>19</v>
@@ -1196,22 +1196,22 @@
         <v>20</v>
       </c>
       <c r="I15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K15" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="L15" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="M15" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="N15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O15" t="s">
         <v>76</v>
@@ -1237,7 +1237,7 @@
         <v>80</v>
       </c>
       <c r="N16" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="O16" t="s">
         <v>81</v>
@@ -1347,7 +1347,7 @@
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
